--- a/kagawa_seishinka_20261023_174416.xlsx
+++ b/kagawa_seishinka_20261023_174416.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,11 +452,6 @@
           <t>問い合わせフォームURL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>精神系診療科目</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,11 +477,6 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,11 +510,6 @@
           <t>https://www.obayashihp.or.jp/contactus.html</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -554,11 +539,6 @@
           <t>https://www.tamamokai.com/%E3%81%8A%E5%95%8F%E3%81%84%E5%90%88%E3%82%8F%E3%81%9B/</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,11 +564,6 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -622,11 +597,6 @@
           <t>https://www.takamatsu-municipal-hospital.jp/archives/45</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,11 +622,6 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -686,11 +651,6 @@
           <t>https://www.ooae.jp/diagnosis#anc04</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -716,11 +676,6 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>児童精神科、精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -746,11 +701,6 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -780,11 +730,6 @@
           <t>https://nishikasuga.com/contact/</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>児童精神科</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -810,11 +755,6 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -836,11 +776,6 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -862,11 +797,6 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -888,11 +818,6 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -914,11 +839,6 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -940,11 +860,6 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -974,11 +889,6 @@
           <t>https://murakawa-clinic.com/contact</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>児童精神科</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1004,11 +914,6 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1038,11 +943,6 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1068,11 +968,6 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1104,11 +999,6 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>https://www.takamatsu.jrc.or.jp/contact/</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>精神科</t>
         </is>
       </c>
     </row>
@@ -1132,11 +1022,6 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1166,11 +1051,6 @@
           <t>https://www.sanko-hp.com/contact/</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>児童精神科、精神科、心療内科、老年精神科</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1196,11 +1076,6 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>精神科、心療内科、老年精神科、老年心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1222,11 +1097,6 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1252,11 +1122,6 @@
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1278,11 +1143,6 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1308,11 +1168,6 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1338,11 +1193,6 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1364,11 +1214,6 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1394,11 +1239,6 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1428,11 +1268,6 @@
           <t>https://www.yui-mental-cl.com/medical-information/</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1458,11 +1293,6 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1492,11 +1322,6 @@
           <t>https://www.enai-mental-clinic.jp/mform/</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1522,11 +1347,6 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>児童精神科、精神科</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1548,11 +1368,6 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1582,11 +1397,6 @@
           <t>https://www.pref.kagawa.lg.jp/marugamebyoin/marugamebyoin/mail.html</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1612,11 +1422,6 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1646,11 +1451,6 @@
           <t>https://yoshida-hp.jimdofree.com/お問い合わせ/</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>老年精神科</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1680,11 +1480,6 @@
           <t>https://www.nishimon-hp.jp/お問い合わせ/</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1710,11 +1505,6 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1740,11 +1530,6 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1778,11 +1563,6 @@
           <t>https://www.sowa-clinic.jp/contact</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>老年精神科</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1816,11 +1596,6 @@
           <t>https://www.kaisei.or.jp/contact/</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1846,11 +1621,6 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>精神科、心療内科、老年精神科、児童・思春期精神科</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1876,11 +1646,6 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1902,11 +1667,6 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1936,11 +1696,6 @@
           <t>http://www.minori-clinic.jp/form/minori-cl/contact-minori</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1970,11 +1725,6 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2000,11 +1750,6 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>児童精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2034,11 +1779,6 @@
           <t>https://mitoyo-hosp.jp/contact.php</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2068,11 +1808,6 @@
           <t>http://shimizu-hospital.net/contact</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>精神科、神経科</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2102,11 +1837,6 @@
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2140,11 +1870,6 @@
           <t>https://www.city.sanuki.lg.jp/cgi-bin/inquiry.php/38?page_no=2426</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2174,11 +1899,6 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2204,11 +1924,6 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2230,11 +1945,6 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2260,11 +1970,6 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2290,11 +1995,6 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2320,11 +2020,6 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2350,11 +2045,6 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2376,11 +2066,6 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2406,11 +2091,6 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2436,11 +2116,6 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2462,11 +2137,6 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2492,11 +2162,6 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2526,11 +2191,6 @@
           <t>https://www.matsuura-kodomo-mental.jp/guide/flow/</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2556,11 +2216,6 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>精神科、心療内科、老年精神科、老年心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2586,11 +2241,6 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>精神科、神経科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2616,11 +2266,6 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>精神科、心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2646,11 +2291,6 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>精神科心療内科</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2672,11 +2312,6 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>精神科</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2702,11 +2337,6 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>心療内科（GMOクリニック・マップ）</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2728,11 +2358,6 @@
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>心療内科（GMOクリニック・マップ）</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2754,11 +2379,6 @@
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>児童精神科（GMOクリニック・マップ）</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2780,11 +2400,6 @@
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>（施設名より精神科系と判断・科目未確認）</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2812,11 +2427,6 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>https://santepeare.com/otoiawase/</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>児童精神科（GMOクリニック・マップ）</t>
         </is>
       </c>
     </row>
